--- a/parameters_variables.xlsx
+++ b/parameters_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\projects\gw_ecosystem_services_Fulda_plain\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susanneschmidt/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A6E178-6A57-49C6-B451-94C8E2BCD47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736ADDDC-5FE4-F04A-8B74-227FB800905C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{8E85E7A9-C450-5844-BD64-77EB6910F2CD}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25820" windowHeight="13900" xr2:uid="{8E85E7A9-C450-5844-BD64-77EB6910F2CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -104,9 +104,9 @@
     </comment>
     <comment ref="J4" authorId="1" shapeId="0" xr:uid="{BC23984A-4BE5-DB42-8CB2-421621628373}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
       </text>
     </comment>
@@ -145,35 +145,35 @@
     </comment>
     <comment ref="X4" authorId="2" shapeId="0" xr:uid="{A973AB73-A4B2-DB42-8CE2-2E9D2BA6D327}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
     <comment ref="AB4" authorId="3" shapeId="0" xr:uid="{B2EEDDFE-EFB6-B841-B3B1-49218DCB8340}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Foulquier 2010 Relating</t>
       </text>
     </comment>
     <comment ref="AG4" authorId="4" shapeId="0" xr:uid="{D83D8722-287D-8543-91DC-DFD968583D4B}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.
-Reply:
+Antwort:
     19.6.25 geändert, siehe SI</t>
       </text>
     </comment>
     <comment ref="J5" authorId="5" shapeId="0" xr:uid="{4DF7EAEC-CD2F-EF4A-9BF0-F3F1E42E4442}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
       </text>
     </comment>
@@ -213,33 +213,33 @@
     </comment>
     <comment ref="X5" authorId="6" shapeId="0" xr:uid="{8B1BECD1-664B-894E-902F-58308D659DA9}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
     <comment ref="AB5" authorId="7" shapeId="0" xr:uid="{944B0A6E-7F35-8040-8354-541096ED2DBE}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Foulquier 2010 Relating</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="8" shapeId="0" xr:uid="{009AF6C5-B9AC-7541-9E56-015D22C54F6F}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
       </text>
     </comment>
     <comment ref="J6" authorId="9" shapeId="0" xr:uid="{0F2B29B9-EE72-C54A-8714-498DD1A3C8E0}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
       </text>
     </comment>
@@ -279,33 +279,33 @@
     </comment>
     <comment ref="X6" authorId="10" shapeId="0" xr:uid="{3C0608B8-171F-064A-822A-A3CC6DDC9FC4}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
     <comment ref="AB6" authorId="11" shapeId="0" xr:uid="{4659E4E8-C0C9-CB4D-BEA9-CCB12CD16D5B}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Foulquier 2010 Relating</t>
       </text>
     </comment>
     <comment ref="AG6" authorId="12" shapeId="0" xr:uid="{B40E02FA-A395-684A-865E-E43D81BF9EF7}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
       </text>
     </comment>
     <comment ref="J7" authorId="13" shapeId="0" xr:uid="{8AB12162-2BF7-9849-9318-3D6AC8CBAB8F}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
       </text>
     </comment>
@@ -345,33 +345,33 @@
     </comment>
     <comment ref="X7" authorId="14" shapeId="0" xr:uid="{D578DC42-15AA-9242-8F7A-DCCCBD7DB327}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
     <comment ref="AB7" authorId="15" shapeId="0" xr:uid="{D9858DC7-D04C-4A4F-872C-0C59D675639A}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Foulquier 2010 Relating</t>
       </text>
     </comment>
     <comment ref="AG7" authorId="16" shapeId="0" xr:uid="{507182A8-A16E-3B46-A78B-C475F7E79FFC}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
       </text>
     </comment>
     <comment ref="J8" authorId="17" shapeId="0" xr:uid="{28910C3F-267C-EF48-8C2C-F6C895522D82}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
       </text>
     </comment>
@@ -411,33 +411,33 @@
     </comment>
     <comment ref="X8" authorId="18" shapeId="0" xr:uid="{E7A076DC-8E76-1148-951F-1F3AE0C081A3}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
     <comment ref="AB8" authorId="19" shapeId="0" xr:uid="{8ABD701E-78D0-4A47-8F33-59280C42BAAB}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Foulquier 2010 Relating</t>
       </text>
     </comment>
     <comment ref="AG8" authorId="20" shapeId="0" xr:uid="{C8D487C4-854D-254E-A24C-BB3F3463062E}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
       </text>
     </comment>
     <comment ref="J9" authorId="21" shapeId="0" xr:uid="{E68EDC32-0C11-F24F-BC92-6599E44DEE2B}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     7.5 g COD per g humic acid derived in SI, and on sheet calculating_COD in this file</t>
       </text>
     </comment>
@@ -477,25 +477,25 @@
     </comment>
     <comment ref="X9" authorId="22" shapeId="0" xr:uid="{03DDDF21-1FDE-1A44-92CB-02C9D1E67681}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     average of Di Lorenzo, Navel, Mermillod-Blondin</t>
       </text>
     </comment>
     <comment ref="AB9" authorId="23" shapeId="0" xr:uid="{74D124C3-18A4-4549-83DD-7E733D9BD57D}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Foulquier 2010 Relating</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="24" shapeId="0" xr:uid="{59162C1A-C9E9-6D46-9F9A-64B6BAFF2CAB}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Equating organic carbon to biofilm, we used the growth rate measured by (Foulquier et al., 2010) of 0.35 µg C bacteria / day and using a biomass molar mass of 24.6 g/mol (see above), 1.05 mol COD/mol biomass (see above) this translates to 1.4939E-08 mol COD bacteria / day. Multiplying with an average COD bacterial dry mass of 1.0e-05 mol COD / L, yields 0.002 / day. Assuming that the maximum growth rate is 10 times as high, we set the the maximum growth rate of fauna on microorganisms to 0.02 / day.</t>
       </text>
     </comment>
@@ -504,7 +504,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="199">
   <si>
     <t>variable_parameter</t>
   </si>
@@ -533,9 +533,6 @@
     <t>m</t>
   </si>
   <si>
-    <t>n NPZD (see separate file same folder) no import</t>
-  </si>
-  <si>
     <t>import_MO_het</t>
   </si>
   <si>
@@ -554,9 +551,6 @@
     <t>acetic_acids_fraction</t>
   </si>
   <si>
-    <t>#assuming acetate makes up 1 % of carboxylic acids</t>
-  </si>
-  <si>
     <t>mortalityRate</t>
   </si>
   <si>
@@ -587,9 +581,6 @@
     <t>rMO_COD_uptake_h_at_lab_temperature</t>
   </si>
   <si>
-    <t>per h # #micro ac</t>
-  </si>
-  <si>
     <t>rMO_COD_uptake_per_day_at_lab_temperature</t>
   </si>
   <si>
@@ -711,12 +702,6 @@
   </si>
   <si>
     <t>growth_model_fauna</t>
-  </si>
-  <si>
-    <t># since it is not easy to extrapolate the parameters from LT50 curves, and since they are often not provided in the literature, very roughly let's assume linear response.</t>
-  </si>
-  <si>
-    <t># Thus: 100% at 12 degrees, between 50 and 100% at 16 degrees, between 0 and50% at 20 degrees (Brielmann 2011). Assuming that half of the fauna population behavoes like amphipods and half like asellids, 100% survival at 12 degrees, (75% survival at 16 degrees,) 25 % at 20 degrees. Taking the endpoint 20 degrees, 0.25 of the population survives aafter an increase by 8 degrees. This means that 0.75 have died. Thus , for each degree of increase, 0.75/8 = 0.09375 , roughly 1 % of the individuals die.    above or below 10 degree</t>
   </si>
   <si>
     <t>molar mass g / mol</t>
@@ -1081,19 +1066,7 @@
     <t>molar mass</t>
   </si>
   <si>
-    <t>2 mol COD / mol acetate. 64 g COD / 60 g acetate, d.h. 1.067 g COD / g acetate, see also acetate biogeochemistry. Warte, her geht’s um die umrechnugn der wachstumsrate. Stop</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> p. 1468 in Gerritse: 4.3 microM;  i.e. mol / L!, und zwar mol acetate, i.e. multiply with 1.07 to get mol COD</t>
-  </si>
-  <si>
     <t xml:space="preserve"> mol COD drymass_MO  mol COD acetate^-1</t>
-  </si>
-  <si>
-    <t>gdrymass_MO  gacetate? Gerritse et al. (1992): 10.6 g- mol-1, d.h. 10.6/24.6 mol biomass / mol acetate - aber ist das dry? " Expressed as grams of cell carbon produced per mole of carbon substrate consumed." wohl wet weight, aber cell carbon ?! Ignoriere ich erst mal. Aber in dry mass muss ich umrechnen. also *0.9. This was multuiiplied iwth 1.07 mol COD / mol biomass and divided by 2 mol COD / mol acetate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6.25 in code auskommentiert - aber dann gehen MO ein .. </t>
   </si>
   <si>
     <r>
@@ -1255,9 +1228,6 @@
     <t>g COD / g biomass</t>
   </si>
   <si>
-    <t>now same as microbes. Alternatively , 0.1 as in Lindeman, but thats less. Lezts stick  the original plan. Thats dry mass alreeady. Alhtough, no, the original plan was acetate - that does not hold for fauna. It barely holds for MO. 0.1</t>
-  </si>
-  <si>
     <t>mortalityFraction_per_degree</t>
   </si>
   <si>
@@ -1440,9 +1410,6 @@
   </si>
   <si>
     <t>average (Di Lorenzo, Navel, Mermillod-Blondin) mol COD / (mol dry mass COD ) / d</t>
-  </si>
-  <si>
-    <t>total unempflich gegenueber mortality</t>
   </si>
   <si>
     <t>multiplied with max measured biomass</t>
@@ -1630,6 +1597,33 @@
   </si>
   <si>
     <t>difference between reference and +3deg C in the River zone per  year,</t>
+  </si>
+  <si>
+    <t>2 mol COD / mol acetate. 64 g COD / 60 g acetate, d.h. 1.067 g COD / g acetate</t>
+  </si>
+  <si>
+    <t>per h</t>
+  </si>
+  <si>
+    <t>assuming acetate makes up 1 % of carboxylic acids</t>
+  </si>
+  <si>
+    <t>in NPZD (Soetaert et al.) no import</t>
+  </si>
+  <si>
+    <t>gdrymass_MO  gacetate; Gerritse et al. (1992): 10.6 g- mol-1, d.h. 10.6/24.6 mol biomass / mol acetate - dry? "Expressed as grams of cell carbon produced per mole of carbon substrate consumed." This was multiplied with 1.07 mol COD / mol biomass and divided by 2 mol COD / mol acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> p. 1468 in Gerritse: 4.3 microM;  i.e. mol / L!,  mol acetate, i.e. multiply with 1.07 to get mol COD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">now same as microbes. Alternatively , 0.1 as in Lindeman, but thats less. This is dry mass </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> since it is not easy to extrapolate the parameters from LT50 curves, and since they are often not provided in the literature, very roughly let's assume linear response.</t>
+  </si>
+  <si>
+    <t>Thus: 100% at 12 degrees, between 50 and 100% at 16 degrees, between 0 and50% at 20 degrees (Brielmann 2011). Assuming that half of the fauna population behavoes like amphipods and half like asellids, 100% survival at 12 degrees, (75% survival at 16 degrees,) 25 % at 20 degrees. Taking the endpoint 20 degrees, 0.25 of the population survives aafter an increase by 8 degrees. This means that 0.75 have died. Thus , for each degree of increase, 0.75/8 = 0.09375 , roughly 1 % of the individuals die.    above or below 10 degree</t>
   </si>
 </sst>
 </file>
@@ -1835,8 +1829,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1907,9 +1901,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1947,7 +1941,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2053,7 +2047,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2195,7 +2189,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2284,7 +2278,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB7B919E-F4BE-8A4F-9679-A3F32BFB830E}">
   <dimension ref="A1:AL9"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -2299,67 +2293,61 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="M1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O1" t="s">
         <v>5</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q1" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="S1" t="s">
-        <v>9</v>
+        <v>193</v>
       </c>
       <c r="U1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V1" t="s">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="W1" t="s">
-        <v>98</v>
+        <v>195</v>
       </c>
       <c r="X1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Y1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="Z1" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="AB1" t="s">
-        <v>112</v>
+        <v>196</v>
       </c>
       <c r="AC1" t="s">
-        <v>160</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="AG1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>159</v>
+        <v>51</v>
       </c>
       <c r="AL1" t="s">
-        <v>69</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:38">
@@ -2370,46 +2358,46 @@
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O2" t="s">
         <v>8</v>
       </c>
       <c r="U2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="W2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="X2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="s">
-        <v>27</v>
+        <v>191</v>
       </c>
       <c r="AE2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AL2" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -2423,109 +2411,109 @@
         <v>4</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L3" t="s">
         <v>34</v>
       </c>
-      <c r="H3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K3" t="s">
-        <v>94</v>
-      </c>
-      <c r="L3" t="s">
-        <v>37</v>
-      </c>
       <c r="M3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O3" t="s">
         <v>6</v>
       </c>
       <c r="P3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="Q3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R3" t="s">
+        <v>12</v>
+      </c>
+      <c r="S3" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" t="s">
+        <v>17</v>
+      </c>
+      <c r="W3" t="s">
+        <v>21</v>
+      </c>
+      <c r="X3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI3" t="s">
         <v>15</v>
       </c>
-      <c r="R3" t="s">
-        <v>13</v>
-      </c>
-      <c r="S3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T3" t="s">
-        <v>67</v>
-      </c>
-      <c r="U3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V3" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" t="s">
-        <v>23</v>
-      </c>
-      <c r="X3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC3" t="s">
+      <c r="AJ3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK3" t="s">
         <v>65</v>
       </c>
-      <c r="AD3" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>29</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>68</v>
-      </c>
       <c r="AL3" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -2585,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="U4">
         <v>30</v>
@@ -2643,7 +2631,7 @@
         <v>1</v>
       </c>
       <c r="AK4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AL4">
         <v>9.375E-2</v>
@@ -2706,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="U5">
         <v>30</v>
@@ -2764,7 +2752,7 @@
         <v>1</v>
       </c>
       <c r="AK5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AL5">
         <v>9.375E-2</v>
@@ -2827,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="U6">
         <v>30</v>
@@ -2885,7 +2873,7 @@
         <v>1</v>
       </c>
       <c r="AK6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AL6">
         <v>9.375E-2</v>
@@ -2948,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="U7">
         <v>30</v>
@@ -3006,7 +2994,7 @@
         <v>1</v>
       </c>
       <c r="AK7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AL7">
         <v>9.375E-2</v>
@@ -3069,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="U8">
         <v>30</v>
@@ -3127,7 +3115,7 @@
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AL8">
         <v>9.375E-2</v>
@@ -3190,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="U9">
         <v>30</v>
@@ -3248,7 +3236,7 @@
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="AL9">
         <v>9.375E-2</v>
@@ -3265,7 +3253,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92644CC1-E167-AE40-81F2-8D9D4BC8EB36}">
   <dimension ref="B1:U139"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16"/>
   <cols>
     <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -3273,7 +3261,7 @@
   <sheetData>
     <row r="1" spans="2:21">
       <c r="B1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="2:21">
@@ -3356,38 +3344,38 @@
     </row>
     <row r="16" spans="2:21">
       <c r="L16" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="12:20">
       <c r="L17" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N17" t="s">
+        <v>42</v>
+      </c>
+      <c r="O17" t="s">
+        <v>46</v>
+      </c>
+      <c r="P17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>44</v>
+      </c>
+      <c r="R17" t="s">
         <v>45</v>
       </c>
-      <c r="O17" t="s">
+      <c r="T17" t="s">
         <v>49</v>
-      </c>
-      <c r="P17" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>47</v>
-      </c>
-      <c r="R17" t="s">
-        <v>48</v>
-      </c>
-      <c r="T17" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="18" spans="12:20">
       <c r="L18" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N18" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="O18">
         <v>9</v>
@@ -3408,12 +3396,12 @@
     </row>
     <row r="19" spans="12:20">
       <c r="L19" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="12:20">
       <c r="L20" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="12:20">
@@ -3422,43 +3410,43 @@
         <v>227</v>
       </c>
       <c r="M21" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="12:20">
       <c r="L22" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="12:20">
       <c r="L25" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="N25" t="s">
+        <v>42</v>
+      </c>
+      <c r="O25" t="s">
+        <v>46</v>
+      </c>
+      <c r="P25" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>44</v>
+      </c>
+      <c r="R25" t="s">
         <v>45</v>
       </c>
-      <c r="O25" t="s">
+      <c r="T25" t="s">
         <v>49</v>
-      </c>
-      <c r="P25" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>47</v>
-      </c>
-      <c r="R25" t="s">
-        <v>48</v>
-      </c>
-      <c r="T25" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="26" spans="12:20">
       <c r="L26" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="N26" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O26">
         <v>2</v>
@@ -3482,53 +3470,53 @@
         <v>60</v>
       </c>
       <c r="M27" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="12:20">
       <c r="L28" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="12:20">
       <c r="L31" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" spans="12:20" ht="17.5">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="32" spans="12:20" ht="18">
       <c r="L32" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="10:20">
       <c r="L33" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="N33" t="s">
+        <v>42</v>
+      </c>
+      <c r="O33" t="s">
+        <v>46</v>
+      </c>
+      <c r="P33" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>44</v>
+      </c>
+      <c r="R33" t="s">
         <v>45</v>
       </c>
-      <c r="O33" t="s">
+      <c r="T33" t="s">
         <v>49</v>
-      </c>
-      <c r="P33" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>47</v>
-      </c>
-      <c r="R33" t="s">
-        <v>48</v>
-      </c>
-      <c r="T33" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="34" spans="10:20">
       <c r="L34" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="N34" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O34">
         <v>1</v>
@@ -3551,7 +3539,7 @@
       <c r="J35" s="11"/>
       <c r="K35" s="10"/>
       <c r="L35" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="10:20">
@@ -3569,7 +3557,7 @@
     </row>
     <row r="40" spans="10:20">
       <c r="M40" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="10:20">
@@ -3577,25 +3565,25 @@
         <v>2.6</v>
       </c>
       <c r="N41" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="P41">
         <v>2.6</v>
       </c>
       <c r="Q41" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="10:20">
       <c r="L42" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="M42">
         <f>12+1.8+0.5*16+0.2*14</f>
         <v>24.6</v>
       </c>
       <c r="N42" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="10:20">
@@ -3606,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="N50" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="3:14">
@@ -3615,10 +3603,10 @@
         <v>0.14336033814723495</v>
       </c>
       <c r="M51" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="N51" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="3:14">
@@ -3627,7 +3615,7 @@
         <v>2.032520325203252E-10</v>
       </c>
       <c r="M54" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="3:14">
@@ -3644,81 +3632,81 @@
     </row>
     <row r="58" spans="3:14">
       <c r="L58" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="59" spans="3:14" ht="17.5">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" ht="18">
       <c r="L59" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="3:14">
       <c r="C60" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D60" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="M60">
         <f>5*12+7+2*16+14</f>
         <v>113</v>
       </c>
       <c r="N60" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="3:14">
       <c r="D61" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E61" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="L61" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="3:14">
       <c r="C62" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D62">
         <v>7.5</v>
       </c>
       <c r="E62" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="L62" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="3:14">
       <c r="C63" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D63">
         <v>5.9</v>
       </c>
       <c r="E63" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="L63" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="3:14">
       <c r="C64" s="13" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D64" s="13">
         <f>D62-D63</f>
         <v>1.5999999999999996</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="F64" s="13"/>
       <c r="K64">
@@ -3726,117 +3714,117 @@
         <v>4.25</v>
       </c>
       <c r="L64" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="3:13">
       <c r="C65" s="13" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D65" s="13">
         <f>D62+D63</f>
         <v>13.4</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="F65" s="13"/>
       <c r="L65" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="3:13">
       <c r="C66" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D66">
         <f>D62/227.172/1000</f>
         <v>3.3014632084940045E-5</v>
       </c>
       <c r="E66" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="L66">
         <f>4.25*32</f>
         <v>136</v>
       </c>
       <c r="M66" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="3:13">
       <c r="C67" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D67">
         <f>D63/227.172/1000</f>
         <v>2.5971510573486172E-5</v>
       </c>
       <c r="E67" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="L67">
         <f>L66/M60</f>
         <v>1.2035398230088497</v>
       </c>
       <c r="M67" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="3:13">
       <c r="C68" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D68">
         <f>D66*24.6</f>
         <v>8.1215994928952515E-4</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="L68" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="69" spans="3:13">
       <c r="C69" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D69">
         <f>D67*24.6</f>
         <v>6.388991601077599E-4</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70" spans="3:13">
       <c r="C70" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D70">
         <f>D68*1.075/1.05</f>
         <v>8.3149709093927569E-4</v>
       </c>
       <c r="E70" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="3:13">
       <c r="C71" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D71">
         <f>D69*1.075/1.05</f>
         <v>6.5411104487223025E-4</v>
       </c>
       <c r="E71" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="3:13">
       <c r="C75" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76" spans="3:13">
@@ -3844,7 +3832,7 @@
         <v>0.33</v>
       </c>
       <c r="E76" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="77" spans="3:13">
@@ -3852,7 +3840,7 @@
         <v>0.73</v>
       </c>
       <c r="E77" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" spans="3:13">
@@ -3861,7 +3849,7 @@
         <v>3.3000000000000002E-7</v>
       </c>
       <c r="E78" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="3:13">
@@ -3870,7 +3858,7 @@
         <v>7.3E-7</v>
       </c>
       <c r="E79" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="3:13">
@@ -3879,7 +3867,7 @@
         <v>2.7500000000000001E-8</v>
       </c>
       <c r="E80" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81" spans="4:12">
@@ -3888,7 +3876,7 @@
         <v>6.0833333333333329E-8</v>
       </c>
       <c r="E81" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="4:12">
@@ -3897,7 +3885,7 @@
         <v>5.5000000000000014E-3</v>
       </c>
       <c r="E82" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="83" spans="4:12">
@@ -3906,7 +3894,7 @@
         <v>1.2166666666666666E-2</v>
       </c>
       <c r="E83" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
     <row r="84" spans="4:12">
@@ -3915,7 +3903,7 @@
         <v>0.13530000000000003</v>
       </c>
       <c r="E84" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="4:12">
@@ -3924,7 +3912,7 @@
         <v>0.29930000000000001</v>
       </c>
       <c r="E85" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="86" spans="4:12">
@@ -3933,7 +3921,7 @@
         <v>0.12885714285714289</v>
       </c>
       <c r="E86" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="4:12">
@@ -3942,7 +3930,7 @@
         <v>0.28504761904761905</v>
       </c>
       <c r="E87" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
     <row r="89" spans="4:12">
@@ -3951,10 +3939,10 @@
         <v>8.4242681454371637E-2</v>
       </c>
       <c r="E89" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="K89" s="16" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="90" spans="4:12">
@@ -3962,13 +3950,13 @@
         <v>6.905E-6</v>
       </c>
       <c r="E90" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="K90">
         <v>0.35</v>
       </c>
       <c r="L90" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
     </row>
     <row r="91" spans="4:12">
@@ -3977,14 +3965,14 @@
         <v>5.8169571544243611E-7</v>
       </c>
       <c r="E91" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="K91">
         <f>K90/1000000/24.6</f>
         <v>1.4227642276422762E-8</v>
       </c>
       <c r="L91" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="92" spans="4:12">
@@ -3993,14 +3981,14 @@
         <v>5.8169571544243611E-7</v>
       </c>
       <c r="E92" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="K92">
         <f>K91*1.05</f>
         <v>1.4939024390243901E-8</v>
       </c>
       <c r="L92" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="93" spans="4:12">
@@ -4009,7 +3997,7 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="L93" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="94" spans="4:12">
@@ -4018,12 +4006,12 @@
         <v>1.4939024390243901E-3</v>
       </c>
       <c r="L94" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="96" spans="4:12">
       <c r="E96" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="97" spans="4:14">
@@ -4031,7 +4019,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="98" spans="4:14">
@@ -4039,13 +4027,13 @@
         <v>9.09</v>
       </c>
       <c r="E98" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F98" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="L98" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
     </row>
     <row r="99" spans="4:14">
@@ -4053,20 +4041,20 @@
         <v>7.58</v>
       </c>
       <c r="E99" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F99" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="L99">
         <f>AVERAGE(D127, D86:D87,D70)</f>
         <v>0.10371468607138892</v>
       </c>
       <c r="M99" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="N99" s="16" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="100" spans="4:14">
@@ -4074,13 +4062,13 @@
         <v>7.96</v>
       </c>
       <c r="E100" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F100" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="N100" s="15" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
     </row>
     <row r="101" spans="4:14">
@@ -4088,10 +4076,10 @@
         <v>6.52</v>
       </c>
       <c r="E101" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F101" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="102" spans="4:14">
@@ -4099,10 +4087,10 @@
         <v>4.71</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F102" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="H102">
         <f>AVERAGE(D102:D105)</f>
@@ -4114,10 +4102,10 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F103" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="104" spans="4:14">
@@ -4125,10 +4113,10 @@
         <v>4.18</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F104" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="105" spans="4:14">
@@ -4136,10 +4124,10 @@
         <v>4.13</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F105" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="106" spans="4:14">
@@ -4147,7 +4135,7 @@
         <v>4.3</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="107" spans="4:14">
@@ -4155,15 +4143,15 @@
         <v>0.5</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="108" spans="4:14">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="108" spans="4:14" ht="20">
       <c r="D108">
         <v>14.9</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
     </row>
     <row r="109" spans="4:14">
@@ -4171,7 +4159,7 @@
         <v>1.9</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
     <row r="110" spans="4:14">
@@ -4179,7 +4167,7 @@
         <v>12.4</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="111" spans="4:14">
@@ -4187,7 +4175,7 @@
         <v>1.2</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="112" spans="4:14">
@@ -4195,7 +4183,7 @@
         <v>0.01</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
     </row>
     <row r="113" spans="4:5">
@@ -4203,7 +4191,7 @@
         <v>8.1</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
     </row>
     <row r="114" spans="4:5">
@@ -4211,12 +4199,12 @@
         <v>0.15336312500000002</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="115" spans="4:5">
       <c r="E115" s="17" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="116" spans="4:5">
@@ -4225,7 +4213,7 @@
         <v>8.3333333333333344E-7</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
     </row>
     <row r="117" spans="4:5">
@@ -4234,7 +4222,7 @@
         <v>6.7499999999999993E-4</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="118" spans="4:5">
@@ -4243,7 +4231,7 @@
         <v>1.2780260416666668E-5</v>
       </c>
       <c r="E118" s="17" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
     </row>
     <row r="119" spans="4:5">
@@ -4252,7 +4240,7 @@
         <v>1.9190174630589144E-7</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="120" spans="4:5">
@@ -4261,7 +4249,7 @@
         <v>1.5544041450777204E-4</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="121" spans="4:5">
@@ -4270,7 +4258,7 @@
         <v>2.9430651506428716E-6</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="122" spans="4:5">
@@ -4279,7 +4267,7 @@
         <v>7.8008839961744482E-6</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
     </row>
     <row r="123" spans="4:5">
@@ -4288,7 +4276,7 @@
         <v>6.3187160369013026E-3</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="124" spans="4:5">
@@ -4297,7 +4285,7 @@
         <v>1.1963679474158013E-4</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125" spans="4:5">
@@ -4306,7 +4294,7 @@
         <v>7.9866193294166962E-6</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
     <row r="126" spans="4:5">
@@ -4315,7 +4303,7 @@
         <v>6.4691616568275231E-3</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="127" spans="4:5">
@@ -4324,12 +4312,12 @@
         <v>1.224852898544749E-4</v>
       </c>
       <c r="E127" s="17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="130" spans="4:6" ht="210">
+      <c r="D130" s="20" t="s">
         <v>183</v>
-      </c>
-    </row>
-    <row r="130" spans="4:6" ht="182">
-      <c r="D130" s="20" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="131" spans="4:6">
@@ -4338,10 +4326,10 @@
         <v>1.6000000000000003E-5</v>
       </c>
       <c r="E131" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="F131" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
     </row>
     <row r="132" spans="4:6">
@@ -4350,10 +4338,10 @@
         <v>4.5714285714285719E-6</v>
       </c>
       <c r="E132" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="F132" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="133" spans="4:6">
@@ -4361,10 +4349,10 @@
         <v>630000</v>
       </c>
       <c r="E133" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="F133" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="134" spans="4:6">
@@ -4373,10 +4361,10 @@
         <v>6.3E+17</v>
       </c>
       <c r="E134" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F134" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="135" spans="4:6">
@@ -4385,10 +4373,10 @@
         <v>2880000000000.0005</v>
       </c>
       <c r="E135" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="F135" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="136" spans="4:6">
@@ -4397,22 +4385,22 @@
         <v>227</v>
       </c>
       <c r="E136" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F136" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="137" spans="4:6">
       <c r="D137">
         <f>D135*D136</f>
-        <v>653760000000000.13</v>
+        <v>653760000000000.12</v>
       </c>
       <c r="E137" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="F137" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="138" spans="4:6">
@@ -4421,10 +4409,10 @@
         <v>653760000000.00012</v>
       </c>
       <c r="E138" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F138" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="139" spans="4:6">
@@ -4433,10 +4421,10 @@
         <v>653760000.00000012</v>
       </c>
       <c r="E139" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F139" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
